--- a/i18n/nl.xlsx
+++ b/i18n/nl.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="12975" tabRatio="500"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -4694,97 +4694,13 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Birds Cards in Hand</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>[invertebrate] in voedselkosten van je vogels</t>
   </si>
   <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
     <t>[fruit] + [seed] in voedselkosten van je vogels</t>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
   </si>
   <si>
     <r>
@@ -4792,6 +4708,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>[rodent] + [fish]</t>
@@ -4801,31 +4718,20 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> in voedselkosten van je vogels</t>
     </r>
   </si>
   <si>
-    <t>No Goal</t>
-  </si>
-  <si>
     <t>Geen doel</t>
   </si>
   <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
     <t>Snavel wijst naar links</t>
   </si>
   <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
     <t>Snavel wijst naar rechts</t>
-  </si>
-  <si>
-    <t>Cubes on "Play a Bird"</t>
   </si>
   <si>
     <r>
@@ -4833,7 +4739,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[cube] op </t>
     </r>
@@ -4842,6 +4749,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>"</t>
@@ -4851,13 +4759,11 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>Speel een vogel"</t>
     </r>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
   </si>
   <si>
     <r>
@@ -4865,7 +4771,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[bird] die </t>
     </r>
@@ -4874,48 +4781,13 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="238"/>
       </rPr>
       <t>≤3[point] waard zijn</t>
     </r>
   </si>
   <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
-    <t>In Forest</t>
-  </si>
-  <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>Translated</t>
   </si>
   <si>
@@ -5714,9 +5586,6 @@
     <t>Bosbeheerder</t>
   </si>
   <si>
-    <t xml:space="preserve">Opeenvolgende vogels in [forest] met op- of aflopende puntenwaarden. </t>
-  </si>
-  <si>
     <t>De puntenwaarde van elke vogel moet hoger zijn dan die van de volgende. Je mag van rechts naar links of van links naar rechts.</t>
   </si>
   <si>
@@ -5735,9 +5604,6 @@
     <t>Weidewachter</t>
   </si>
   <si>
-    <t xml:space="preserve">Opeenvolgende vogels in [grassland] met op- of aflopende puntenwaarden. </t>
-  </si>
-  <si>
     <t>Uilebalanalist</t>
   </si>
   <si>
@@ -5765,12 +5631,6 @@
     <t>Moeraswachter</t>
   </si>
   <si>
-    <t xml:space="preserve">Opeenvolgende vogels in [wetland] met op- of aflopende puntenwaarden. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wintervoeder </t>
-  </si>
-  <si>
     <t>Voedsel in je voorraad aan het einde van het spel</t>
   </si>
   <si>
@@ -5886,6 +5746,153 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Opeenvolgende vogels in [forest] met op- of aflopende puntenwaarden.</t>
+  </si>
+  <si>
+    <t>Opeenvolgende vogels in [grassland] met op- of aflopende puntenwaarden.</t>
+  </si>
+  <si>
+    <t>Opeenvolgende vogels in [wetland] met op- of aflopende puntenwaarden.</t>
+  </si>
+  <si>
+    <t>Wintervoeder</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
 </sst>
 </file>
@@ -5895,7 +5902,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;PRAWDA&quot;;&quot;PRAWDA&quot;;&quot;FAŁSZ&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5914,25 +5921,35 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5955,7 +5972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5982,6 +5999,8 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6191,7 +6210,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1926</v>
+        <v>1877</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -7039,7 +7058,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1890</v>
+        <v>1841</v>
       </c>
       <c r="C34" t="s">
         <v>137</v>
@@ -8896,7 +8915,7 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>1891</v>
+        <v>1842</v>
       </c>
       <c r="C106" t="s">
         <v>391</v>
@@ -9750,7 +9769,7 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>1893</v>
+        <v>1844</v>
       </c>
       <c r="C139" t="s">
         <v>510</v>
@@ -10758,7 +10777,7 @@
         <v>651</v>
       </c>
       <c r="C179" t="s">
-        <v>1894</v>
+        <v>1845</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>13</v>
@@ -12941,10 +12960,10 @@
         <v>924</v>
       </c>
       <c r="E263" t="s">
-        <v>1897</v>
+        <v>1848</v>
       </c>
       <c r="F263" t="s">
-        <v>1618</v>
+        <v>1573</v>
       </c>
       <c r="I263" s="1"/>
       <c r="J263" s="1"/>
@@ -12970,7 +12989,7 @@
         <v>927</v>
       </c>
       <c r="F264" t="s">
-        <v>1619</v>
+        <v>1574</v>
       </c>
       <c r="I264" s="1"/>
       <c r="J264" s="1" t="s">
@@ -12996,7 +13015,7 @@
         <v>930</v>
       </c>
       <c r="F265" t="s">
-        <v>1620</v>
+        <v>1575</v>
       </c>
       <c r="I265" s="1"/>
       <c r="J265" s="1" t="s">
@@ -13022,7 +13041,7 @@
         <v>933</v>
       </c>
       <c r="F266" t="s">
-        <v>1898</v>
+        <v>1849</v>
       </c>
       <c r="I266" s="1"/>
       <c r="J266" s="1" t="s">
@@ -13045,7 +13064,7 @@
         <v>924</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1899</v>
+        <v>1850</v>
       </c>
       <c r="F267" t="s">
         <v>936</v>
@@ -13074,7 +13093,7 @@
         <v>939</v>
       </c>
       <c r="F268" t="s">
-        <v>1621</v>
+        <v>1576</v>
       </c>
       <c r="I268" s="1"/>
       <c r="J268" s="1" t="s">
@@ -13100,7 +13119,7 @@
         <v>942</v>
       </c>
       <c r="F269" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="I269" s="1"/>
       <c r="J269" s="1" t="s">
@@ -13126,7 +13145,7 @@
         <v>945</v>
       </c>
       <c r="F270" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="I270" s="1"/>
       <c r="J270" s="1" t="s">
@@ -13152,7 +13171,7 @@
         <v>948</v>
       </c>
       <c r="F271" t="s">
-        <v>1624</v>
+        <v>1579</v>
       </c>
       <c r="I271" s="1"/>
       <c r="J271" s="1" t="s">
@@ -13178,7 +13197,7 @@
         <v>951</v>
       </c>
       <c r="F272" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="I272" s="1"/>
       <c r="J272" s="1" t="s">
@@ -13204,7 +13223,7 @@
         <v>954</v>
       </c>
       <c r="F273" t="s">
-        <v>1626</v>
+        <v>1581</v>
       </c>
       <c r="I273" s="1"/>
       <c r="J273" s="1"/>
@@ -13230,7 +13249,7 @@
         <v>957</v>
       </c>
       <c r="F274" t="s">
-        <v>1627</v>
+        <v>1582</v>
       </c>
       <c r="I274" s="1"/>
       <c r="J274" s="1"/>
@@ -13256,7 +13275,7 @@
         <v>960</v>
       </c>
       <c r="F275" t="s">
-        <v>1628</v>
+        <v>1583</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>20</v>
@@ -13284,7 +13303,7 @@
         <v>963</v>
       </c>
       <c r="F276" t="s">
-        <v>1900</v>
+        <v>1851</v>
       </c>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
@@ -13310,7 +13329,7 @@
         <v>966</v>
       </c>
       <c r="F277" t="s">
-        <v>1629</v>
+        <v>1584</v>
       </c>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
@@ -13334,7 +13353,7 @@
         <v>969</v>
       </c>
       <c r="F278" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
@@ -13360,7 +13379,7 @@
         <v>972</v>
       </c>
       <c r="F279" t="s">
-        <v>1631</v>
+        <v>1586</v>
       </c>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
@@ -13384,7 +13403,7 @@
         <v>975</v>
       </c>
       <c r="F280" t="s">
-        <v>1632</v>
+        <v>1587</v>
       </c>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
@@ -13408,7 +13427,7 @@
         <v>978</v>
       </c>
       <c r="F281" t="s">
-        <v>1633</v>
+        <v>1588</v>
       </c>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
@@ -13434,7 +13453,7 @@
         <v>981</v>
       </c>
       <c r="F282" t="s">
-        <v>1634</v>
+        <v>1589</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>20</v>
@@ -13460,7 +13479,7 @@
         <v>984</v>
       </c>
       <c r="F283" t="s">
-        <v>1901</v>
+        <v>1852</v>
       </c>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
@@ -13486,7 +13505,7 @@
         <v>987</v>
       </c>
       <c r="F284" t="s">
-        <v>1902</v>
+        <v>1853</v>
       </c>
       <c r="I284" s="1"/>
       <c r="J284" s="1" t="s">
@@ -13514,7 +13533,7 @@
         <v>990</v>
       </c>
       <c r="F285" t="s">
-        <v>1635</v>
+        <v>1590</v>
       </c>
       <c r="I285" s="1"/>
       <c r="J285" s="1" t="s">
@@ -13540,7 +13559,7 @@
         <v>993</v>
       </c>
       <c r="F286" t="s">
-        <v>1903</v>
+        <v>1854</v>
       </c>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
@@ -13561,10 +13580,10 @@
         <v>924</v>
       </c>
       <c r="E287" t="s">
-        <v>1636</v>
+        <v>1591</v>
       </c>
       <c r="F287" t="s">
-        <v>1637</v>
+        <v>1592</v>
       </c>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
@@ -13588,7 +13607,7 @@
         <v>998</v>
       </c>
       <c r="F288" t="s">
-        <v>1638</v>
+        <v>1593</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>20</v>
@@ -13616,7 +13635,7 @@
         <v>1001</v>
       </c>
       <c r="F289" t="s">
-        <v>1639</v>
+        <v>1594</v>
       </c>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
@@ -13642,7 +13661,7 @@
         <v>1004</v>
       </c>
       <c r="F290" t="s">
-        <v>1640</v>
+        <v>1595</v>
       </c>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
@@ -13668,7 +13687,7 @@
         <v>1007</v>
       </c>
       <c r="F291" t="s">
-        <v>1641</v>
+        <v>1596</v>
       </c>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
@@ -13694,7 +13713,7 @@
         <v>1010</v>
       </c>
       <c r="F292" t="s">
-        <v>1642</v>
+        <v>1597</v>
       </c>
       <c r="I292" s="1"/>
       <c r="J292" s="1"/>
@@ -13720,7 +13739,7 @@
         <v>1013</v>
       </c>
       <c r="F293" t="s">
-        <v>1643</v>
+        <v>1598</v>
       </c>
       <c r="I293" s="1"/>
       <c r="J293" s="1"/>
@@ -13746,7 +13765,7 @@
         <v>1016</v>
       </c>
       <c r="F294" t="s">
-        <v>1644</v>
+        <v>1599</v>
       </c>
       <c r="I294" s="1"/>
       <c r="J294" s="1"/>
@@ -13772,7 +13791,7 @@
         <v>1019</v>
       </c>
       <c r="F295" t="s">
-        <v>1645</v>
+        <v>1600</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>20</v>
@@ -13800,7 +13819,7 @@
         <v>1022</v>
       </c>
       <c r="F296" t="s">
-        <v>1904</v>
+        <v>1855</v>
       </c>
       <c r="I296" s="1"/>
       <c r="J296" s="1"/>
@@ -13828,7 +13847,7 @@
         <v>1025</v>
       </c>
       <c r="F297" t="s">
-        <v>1646</v>
+        <v>1601</v>
       </c>
       <c r="I297" s="1"/>
       <c r="J297" s="1"/>
@@ -13842,7 +13861,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="12" t="s">
-        <v>1896</v>
+        <v>1847</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>1026</v>
@@ -13854,7 +13873,7 @@
         <v>1027</v>
       </c>
       <c r="F298" t="s">
-        <v>1647</v>
+        <v>1602</v>
       </c>
       <c r="I298" s="1"/>
       <c r="J298" s="1"/>
@@ -13878,7 +13897,7 @@
         <v>1028</v>
       </c>
       <c r="F299" t="s">
-        <v>1905</v>
+        <v>1856</v>
       </c>
       <c r="I299" s="1"/>
       <c r="J299" s="1"/>
@@ -13902,7 +13921,7 @@
         <v>1032</v>
       </c>
       <c r="F300" t="s">
-        <v>1648</v>
+        <v>1603</v>
       </c>
       <c r="I300" s="1"/>
       <c r="J300" s="1"/>
@@ -13926,7 +13945,7 @@
         <v>1035</v>
       </c>
       <c r="F301" t="s">
-        <v>1906</v>
+        <v>1857</v>
       </c>
       <c r="I301" s="1"/>
       <c r="J301" s="1"/>
@@ -13950,7 +13969,7 @@
         <v>1038</v>
       </c>
       <c r="F302" t="s">
-        <v>1649</v>
+        <v>1604</v>
       </c>
       <c r="I302" s="1"/>
       <c r="J302" s="1"/>
@@ -13974,7 +13993,7 @@
         <v>1041</v>
       </c>
       <c r="F303" t="s">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
@@ -13998,7 +14017,7 @@
         <v>1044</v>
       </c>
       <c r="F304" t="s">
-        <v>1651</v>
+        <v>1606</v>
       </c>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
@@ -14022,7 +14041,7 @@
         <v>1047</v>
       </c>
       <c r="F305" t="s">
-        <v>1652</v>
+        <v>1607</v>
       </c>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
@@ -14048,7 +14067,7 @@
         <v>1050</v>
       </c>
       <c r="F306" t="s">
-        <v>1925</v>
+        <v>1876</v>
       </c>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
@@ -14072,7 +14091,7 @@
         <v>1053</v>
       </c>
       <c r="F307" t="s">
-        <v>1653</v>
+        <v>1608</v>
       </c>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
@@ -14096,7 +14115,7 @@
         <v>1056</v>
       </c>
       <c r="F308" t="s">
-        <v>1654</v>
+        <v>1609</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -14120,7 +14139,7 @@
         <v>1059</v>
       </c>
       <c r="F309" t="s">
-        <v>1655</v>
+        <v>1610</v>
       </c>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
@@ -14146,7 +14165,7 @@
         <v>1062</v>
       </c>
       <c r="F310" t="s">
-        <v>1656</v>
+        <v>1611</v>
       </c>
       <c r="I310" s="1"/>
       <c r="J310" s="1" t="s">
@@ -14184,7 +14203,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1892</v>
+        <v>1843</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>1066</v>
@@ -14196,7 +14215,7 @@
         <v>1067</v>
       </c>
       <c r="F312" t="s">
-        <v>1657</v>
+        <v>1612</v>
       </c>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
@@ -14220,7 +14239,7 @@
         <v>1070</v>
       </c>
       <c r="F313" t="s">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>20</v>
@@ -14246,7 +14265,7 @@
         <v>1073</v>
       </c>
       <c r="F314" t="s">
-        <v>1658</v>
+        <v>1613</v>
       </c>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
@@ -14270,7 +14289,7 @@
         <v>1076</v>
       </c>
       <c r="F315" t="s">
-        <v>1659</v>
+        <v>1614</v>
       </c>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
@@ -14294,7 +14313,7 @@
         <v>1079</v>
       </c>
       <c r="F316" t="s">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="I316" s="1"/>
       <c r="J316" s="1" t="s">
@@ -14320,7 +14339,7 @@
         <v>1082</v>
       </c>
       <c r="F317" t="s">
-        <v>1907</v>
+        <v>1858</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -14344,7 +14363,7 @@
         <v>1085</v>
       </c>
       <c r="F318" t="s">
-        <v>1661</v>
+        <v>1616</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1" t="s">
@@ -14372,7 +14391,7 @@
         <v>1088</v>
       </c>
       <c r="F319" t="s">
-        <v>1656</v>
+        <v>1611</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>20</v>
@@ -14402,7 +14421,7 @@
         <v>1091</v>
       </c>
       <c r="F320" t="s">
-        <v>1662</v>
+        <v>1617</v>
       </c>
       <c r="I320" s="1"/>
       <c r="J320" s="1" t="s">
@@ -14430,7 +14449,7 @@
         <v>1094</v>
       </c>
       <c r="F321" t="s">
-        <v>1663</v>
+        <v>1618</v>
       </c>
       <c r="I321" s="1"/>
       <c r="J321" s="1"/>
@@ -14454,7 +14473,7 @@
         <v>1097</v>
       </c>
       <c r="F322" t="s">
-        <v>1664</v>
+        <v>1619</v>
       </c>
       <c r="I322" s="1"/>
       <c r="J322" s="1"/>
@@ -14480,7 +14499,7 @@
         <v>1100</v>
       </c>
       <c r="F323" t="s">
-        <v>1665</v>
+        <v>1620</v>
       </c>
       <c r="I323" s="1"/>
       <c r="J323" s="1"/>
@@ -14504,7 +14523,7 @@
         <v>1103</v>
       </c>
       <c r="F324" t="s">
-        <v>1640</v>
+        <v>1595</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>20</v>
@@ -14532,7 +14551,7 @@
         <v>1106</v>
       </c>
       <c r="F325" t="s">
-        <v>1908</v>
+        <v>1859</v>
       </c>
       <c r="I325" s="1"/>
       <c r="J325" s="1" t="s">
@@ -14560,7 +14579,7 @@
         <v>1109</v>
       </c>
       <c r="F326" t="s">
-        <v>1666</v>
+        <v>1621</v>
       </c>
       <c r="I326" s="1"/>
       <c r="J326" s="1"/>
@@ -14584,7 +14603,7 @@
         <v>1112</v>
       </c>
       <c r="F327" t="s">
-        <v>1667</v>
+        <v>1622</v>
       </c>
       <c r="I327" s="1"/>
       <c r="J327" s="1"/>
@@ -14608,7 +14627,7 @@
         <v>1115</v>
       </c>
       <c r="F328" t="s">
-        <v>1668</v>
+        <v>1623</v>
       </c>
       <c r="I328" s="1"/>
       <c r="J328" s="1"/>
@@ -14632,7 +14651,7 @@
         <v>1118</v>
       </c>
       <c r="F329" t="s">
-        <v>1669</v>
+        <v>1624</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>20</v>
@@ -14660,7 +14679,7 @@
         <v>1121</v>
       </c>
       <c r="F330" t="s">
-        <v>1670</v>
+        <v>1625</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>20</v>
@@ -14688,7 +14707,7 @@
         <v>1124</v>
       </c>
       <c r="F331" t="s">
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>20</v>
@@ -14716,7 +14735,7 @@
         <v>1127</v>
       </c>
       <c r="F332" t="s">
-        <v>1672</v>
+        <v>1627</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>20</v>
@@ -14744,7 +14763,7 @@
         <v>1130</v>
       </c>
       <c r="F333" t="s">
-        <v>1673</v>
+        <v>1628</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>20</v>
@@ -14772,7 +14791,7 @@
         <v>1133</v>
       </c>
       <c r="F334" t="s">
-        <v>1652</v>
+        <v>1607</v>
       </c>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
@@ -14796,7 +14815,7 @@
         <v>1136</v>
       </c>
       <c r="F335" t="s">
-        <v>1909</v>
+        <v>1860</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>20</v>
@@ -14822,7 +14841,7 @@
         <v>1139</v>
       </c>
       <c r="F336" t="s">
-        <v>1674</v>
+        <v>1629</v>
       </c>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
@@ -14848,7 +14867,7 @@
         <v>1142</v>
       </c>
       <c r="F337" t="s">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
@@ -14874,7 +14893,7 @@
         <v>1145</v>
       </c>
       <c r="F338" t="s">
-        <v>1676</v>
+        <v>1631</v>
       </c>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
@@ -14900,7 +14919,7 @@
         <v>1148</v>
       </c>
       <c r="F339" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
@@ -14921,10 +14940,10 @@
         <v>924</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>1910</v>
+        <v>1861</v>
       </c>
       <c r="F340" t="s">
-        <v>1678</v>
+        <v>1633</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>20</v>
@@ -14952,7 +14971,7 @@
         <v>1153</v>
       </c>
       <c r="F341" t="s">
-        <v>1679</v>
+        <v>1634</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1" t="s">
@@ -14978,7 +14997,7 @@
         <v>1156</v>
       </c>
       <c r="F342" t="s">
-        <v>1680</v>
+        <v>1635</v>
       </c>
       <c r="I342" s="1"/>
       <c r="J342" s="1" t="s">
@@ -15004,7 +15023,7 @@
         <v>1159</v>
       </c>
       <c r="F343" t="s">
-        <v>1681</v>
+        <v>1636</v>
       </c>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
@@ -15028,7 +15047,7 @@
         <v>1162</v>
       </c>
       <c r="F344" t="s">
-        <v>1682</v>
+        <v>1637</v>
       </c>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
@@ -15052,7 +15071,7 @@
         <v>1165</v>
       </c>
       <c r="F345" t="s">
-        <v>1683</v>
+        <v>1638</v>
       </c>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
@@ -15076,7 +15095,7 @@
         <v>1168</v>
       </c>
       <c r="F346" t="s">
-        <v>1684</v>
+        <v>1639</v>
       </c>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
@@ -15100,7 +15119,7 @@
         <v>1171</v>
       </c>
       <c r="F347" t="s">
-        <v>1685</v>
+        <v>1640</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>20</v>
@@ -15128,7 +15147,7 @@
         <v>1174</v>
       </c>
       <c r="F348" t="s">
-        <v>1686</v>
+        <v>1641</v>
       </c>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
@@ -15154,7 +15173,7 @@
         <v>1177</v>
       </c>
       <c r="F349" t="s">
-        <v>1687</v>
+        <v>1642</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>20</v>
@@ -15184,7 +15203,7 @@
         <v>1180</v>
       </c>
       <c r="F350" t="s">
-        <v>1911</v>
+        <v>1862</v>
       </c>
       <c r="I350" s="1"/>
       <c r="J350" s="1"/>
@@ -15208,7 +15227,7 @@
         <v>1183</v>
       </c>
       <c r="F351" t="s">
-        <v>1688</v>
+        <v>1643</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>20</v>
@@ -15234,7 +15253,7 @@
         <v>1186</v>
       </c>
       <c r="F352" t="s">
-        <v>1689</v>
+        <v>1644</v>
       </c>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
@@ -15258,7 +15277,7 @@
         <v>1189</v>
       </c>
       <c r="F353" t="s">
-        <v>1690</v>
+        <v>1645</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>20</v>
@@ -15288,7 +15307,7 @@
         <v>1192</v>
       </c>
       <c r="F354" t="s">
-        <v>1691</v>
+        <v>1646</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>20</v>
@@ -15316,7 +15335,7 @@
         <v>1195</v>
       </c>
       <c r="F355" t="s">
-        <v>1692</v>
+        <v>1647</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>20</v>
@@ -15344,7 +15363,7 @@
         <v>1198</v>
       </c>
       <c r="F356" t="s">
-        <v>1912</v>
+        <v>1863</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>20</v>
@@ -15372,7 +15391,7 @@
         <v>1201</v>
       </c>
       <c r="F357" t="s">
-        <v>1913</v>
+        <v>1864</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>20</v>
@@ -15395,10 +15414,10 @@
         <v>1204</v>
       </c>
       <c r="E358" t="s">
-        <v>1693</v>
+        <v>1648</v>
       </c>
       <c r="F358" t="s">
-        <v>1914</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.25">
@@ -15415,10 +15434,10 @@
         <v>1204</v>
       </c>
       <c r="E359" t="s">
-        <v>1694</v>
+        <v>1649</v>
       </c>
       <c r="F359" t="s">
-        <v>1915</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
@@ -15435,10 +15454,10 @@
         <v>1204</v>
       </c>
       <c r="E360" t="s">
-        <v>1695</v>
+        <v>1650</v>
       </c>
       <c r="F360" t="s">
-        <v>1916</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.25">
@@ -15455,10 +15474,10 @@
         <v>1204</v>
       </c>
       <c r="E361" t="s">
-        <v>1696</v>
+        <v>1651</v>
       </c>
       <c r="F361" t="s">
-        <v>1697</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.25">
@@ -15475,10 +15494,10 @@
         <v>1204</v>
       </c>
       <c r="E362" t="s">
-        <v>1698</v>
+        <v>1653</v>
       </c>
       <c r="F362" t="s">
-        <v>1699</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.25">
@@ -15495,10 +15514,10 @@
         <v>1204</v>
       </c>
       <c r="E363" t="s">
-        <v>1700</v>
+        <v>1655</v>
       </c>
       <c r="F363" t="s">
-        <v>1701</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
@@ -15515,10 +15534,10 @@
         <v>1204</v>
       </c>
       <c r="E364" t="s">
-        <v>1702</v>
+        <v>1657</v>
       </c>
       <c r="F364" t="s">
-        <v>1917</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
@@ -15535,10 +15554,10 @@
         <v>1204</v>
       </c>
       <c r="E365" t="s">
-        <v>1703</v>
+        <v>1658</v>
       </c>
       <c r="F365" t="s">
-        <v>1704</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
@@ -15558,7 +15577,7 @@
         <v>1221</v>
       </c>
       <c r="F366" t="s">
-        <v>1705</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
@@ -15575,10 +15594,10 @@
         <v>1204</v>
       </c>
       <c r="E367" t="s">
-        <v>1706</v>
+        <v>1661</v>
       </c>
       <c r="F367" t="s">
-        <v>1707</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
@@ -15595,10 +15614,10 @@
         <v>1204</v>
       </c>
       <c r="E368" t="s">
-        <v>1708</v>
+        <v>1663</v>
       </c>
       <c r="F368" t="s">
-        <v>1709</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -15615,10 +15634,10 @@
         <v>1204</v>
       </c>
       <c r="E369" t="s">
-        <v>1710</v>
+        <v>1665</v>
       </c>
       <c r="F369" t="s">
-        <v>1711</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -15635,10 +15654,10 @@
         <v>1204</v>
       </c>
       <c r="E370" t="s">
-        <v>1712</v>
+        <v>1667</v>
       </c>
       <c r="F370" t="s">
-        <v>1713</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -15655,10 +15674,10 @@
         <v>1204</v>
       </c>
       <c r="E371" t="s">
-        <v>1714</v>
+        <v>1669</v>
       </c>
       <c r="F371" t="s">
-        <v>1715</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -15675,10 +15694,10 @@
         <v>1204</v>
       </c>
       <c r="E372" t="s">
-        <v>1716</v>
+        <v>1671</v>
       </c>
       <c r="F372" t="s">
-        <v>1918</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -15695,10 +15714,10 @@
         <v>1204</v>
       </c>
       <c r="E373" t="s">
-        <v>1717</v>
+        <v>1672</v>
       </c>
       <c r="F373" t="s">
-        <v>1718</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -15715,10 +15734,10 @@
         <v>1204</v>
       </c>
       <c r="E374" t="s">
-        <v>1719</v>
+        <v>1674</v>
       </c>
       <c r="F374" t="s">
-        <v>1720</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -15735,10 +15754,10 @@
         <v>1204</v>
       </c>
       <c r="E375" t="s">
-        <v>1721</v>
+        <v>1676</v>
       </c>
       <c r="F375" t="s">
-        <v>1722</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -15755,7 +15774,7 @@
         <v>1204</v>
       </c>
       <c r="E376" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="F376" t="s">
         <v>571</v>
@@ -15775,10 +15794,10 @@
         <v>1204</v>
       </c>
       <c r="E377" t="s">
-        <v>1724</v>
+        <v>1679</v>
       </c>
       <c r="F377" t="s">
-        <v>1725</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -15795,10 +15814,10 @@
         <v>1204</v>
       </c>
       <c r="E378" t="s">
-        <v>1726</v>
+        <v>1681</v>
       </c>
       <c r="F378" t="s">
-        <v>1727</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -15815,10 +15834,10 @@
         <v>1204</v>
       </c>
       <c r="E379" t="s">
-        <v>1728</v>
+        <v>1683</v>
       </c>
       <c r="F379" t="s">
-        <v>1729</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -15835,10 +15854,10 @@
         <v>1204</v>
       </c>
       <c r="E380" t="s">
-        <v>1730</v>
+        <v>1685</v>
       </c>
       <c r="F380" t="s">
-        <v>1731</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -15855,7 +15874,7 @@
         <v>1204</v>
       </c>
       <c r="E381" t="s">
-        <v>1732</v>
+        <v>1687</v>
       </c>
       <c r="F381" t="s">
         <v>767</v>
@@ -15895,10 +15914,10 @@
         <v>1204</v>
       </c>
       <c r="E383" t="s">
-        <v>1733</v>
+        <v>1688</v>
       </c>
       <c r="F383" t="s">
-        <v>1734</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -15915,10 +15934,10 @@
         <v>1204</v>
       </c>
       <c r="E384" t="s">
-        <v>1735</v>
+        <v>1690</v>
       </c>
       <c r="F384" t="s">
-        <v>1736</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -15935,10 +15954,10 @@
         <v>1204</v>
       </c>
       <c r="E385" t="s">
-        <v>1737</v>
+        <v>1692</v>
       </c>
       <c r="F385" t="s">
-        <v>1738</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -15955,10 +15974,10 @@
         <v>1204</v>
       </c>
       <c r="E386" t="s">
-        <v>1739</v>
+        <v>1694</v>
       </c>
       <c r="F386" t="s">
-        <v>1919</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -15975,10 +15994,10 @@
         <v>1204</v>
       </c>
       <c r="E387" t="s">
-        <v>1740</v>
+        <v>1695</v>
       </c>
       <c r="F387" t="s">
-        <v>1741</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -15995,10 +16014,10 @@
         <v>1204</v>
       </c>
       <c r="E388" t="s">
-        <v>1742</v>
+        <v>1697</v>
       </c>
       <c r="F388" t="s">
-        <v>1743</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -16015,10 +16034,10 @@
         <v>1204</v>
       </c>
       <c r="E389" t="s">
-        <v>1744</v>
+        <v>1699</v>
       </c>
       <c r="F389" t="s">
-        <v>1745</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -16035,10 +16054,10 @@
         <v>1204</v>
       </c>
       <c r="E390" t="s">
-        <v>1746</v>
+        <v>1701</v>
       </c>
       <c r="F390" t="s">
-        <v>1747</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -16058,7 +16077,7 @@
         <v>1272</v>
       </c>
       <c r="F391" t="s">
-        <v>1748</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -16075,10 +16094,10 @@
         <v>1204</v>
       </c>
       <c r="E392" t="s">
-        <v>1749</v>
+        <v>1704</v>
       </c>
       <c r="F392" t="s">
-        <v>1750</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -16115,10 +16134,10 @@
         <v>1204</v>
       </c>
       <c r="E394" t="s">
-        <v>1751</v>
+        <v>1706</v>
       </c>
       <c r="F394" t="s">
-        <v>1752</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -16135,10 +16154,10 @@
         <v>1204</v>
       </c>
       <c r="E395" t="s">
-        <v>1753</v>
+        <v>1708</v>
       </c>
       <c r="F395" t="s">
-        <v>1754</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -16155,10 +16174,10 @@
         <v>1204</v>
       </c>
       <c r="E396" t="s">
-        <v>1755</v>
+        <v>1710</v>
       </c>
       <c r="F396" t="s">
-        <v>1756</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -16175,10 +16194,10 @@
         <v>1204</v>
       </c>
       <c r="E397" t="s">
-        <v>1757</v>
+        <v>1712</v>
       </c>
       <c r="F397" t="s">
-        <v>1758</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -16195,10 +16214,10 @@
         <v>1204</v>
       </c>
       <c r="E398" t="s">
-        <v>1759</v>
+        <v>1714</v>
       </c>
       <c r="F398" t="s">
-        <v>1760</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -16209,16 +16228,16 @@
         <v>1290</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>1895</v>
+        <v>1846</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>1204</v>
       </c>
       <c r="E399" t="s">
-        <v>1761</v>
+        <v>1716</v>
       </c>
       <c r="F399" t="s">
-        <v>1762</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -16235,10 +16254,10 @@
         <v>1204</v>
       </c>
       <c r="E400" t="s">
-        <v>1763</v>
+        <v>1718</v>
       </c>
       <c r="F400" t="s">
-        <v>1764</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -16255,10 +16274,10 @@
         <v>1204</v>
       </c>
       <c r="E401" t="s">
-        <v>1765</v>
+        <v>1720</v>
       </c>
       <c r="F401" t="s">
-        <v>1766</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -16275,10 +16294,10 @@
         <v>1204</v>
       </c>
       <c r="E402" t="s">
-        <v>1767</v>
+        <v>1722</v>
       </c>
       <c r="F402" t="s">
-        <v>1768</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -16295,10 +16314,10 @@
         <v>1204</v>
       </c>
       <c r="E403" t="s">
-        <v>1769</v>
+        <v>1724</v>
       </c>
       <c r="F403" t="s">
-        <v>1770</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -16315,10 +16334,10 @@
         <v>1204</v>
       </c>
       <c r="E404" t="s">
-        <v>1771</v>
+        <v>1726</v>
       </c>
       <c r="F404" t="s">
-        <v>1772</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -16335,10 +16354,10 @@
         <v>1204</v>
       </c>
       <c r="E405" t="s">
-        <v>1773</v>
+        <v>1728</v>
       </c>
       <c r="F405" t="s">
-        <v>1774</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -16355,10 +16374,10 @@
         <v>1204</v>
       </c>
       <c r="E406" t="s">
-        <v>1775</v>
+        <v>1730</v>
       </c>
       <c r="F406" t="s">
-        <v>1776</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -16375,10 +16394,10 @@
         <v>1204</v>
       </c>
       <c r="E407" t="s">
-        <v>1777</v>
+        <v>1732</v>
       </c>
       <c r="F407" t="s">
-        <v>1778</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -16395,10 +16414,10 @@
         <v>1204</v>
       </c>
       <c r="E408" t="s">
-        <v>1779</v>
+        <v>1734</v>
       </c>
       <c r="F408" t="s">
-        <v>1780</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -16415,10 +16434,10 @@
         <v>1204</v>
       </c>
       <c r="E409" t="s">
-        <v>1781</v>
+        <v>1736</v>
       </c>
       <c r="F409" t="s">
-        <v>1782</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -16435,10 +16454,10 @@
         <v>1204</v>
       </c>
       <c r="E410" t="s">
-        <v>1783</v>
+        <v>1738</v>
       </c>
       <c r="F410" t="s">
-        <v>1920</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -16455,10 +16474,10 @@
         <v>1204</v>
       </c>
       <c r="E411" t="s">
-        <v>1784</v>
+        <v>1739</v>
       </c>
       <c r="F411" t="s">
-        <v>1785</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -16475,10 +16494,10 @@
         <v>1204</v>
       </c>
       <c r="E412" t="s">
-        <v>1786</v>
+        <v>1741</v>
       </c>
       <c r="F412" t="s">
-        <v>1787</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -16495,10 +16514,10 @@
         <v>1204</v>
       </c>
       <c r="E413" t="s">
-        <v>1788</v>
+        <v>1743</v>
       </c>
       <c r="F413" t="s">
-        <v>1789</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -16515,10 +16534,10 @@
         <v>1204</v>
       </c>
       <c r="E414" t="s">
-        <v>1790</v>
+        <v>1745</v>
       </c>
       <c r="F414" t="s">
-        <v>1791</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -16535,10 +16554,10 @@
         <v>1204</v>
       </c>
       <c r="E415" t="s">
-        <v>1792</v>
+        <v>1747</v>
       </c>
       <c r="F415" t="s">
-        <v>1921</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -16555,10 +16574,10 @@
         <v>1204</v>
       </c>
       <c r="E416" t="s">
-        <v>1793</v>
+        <v>1748</v>
       </c>
       <c r="F416" t="s">
-        <v>1794</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -16575,10 +16594,10 @@
         <v>1204</v>
       </c>
       <c r="E417" t="s">
-        <v>1795</v>
+        <v>1750</v>
       </c>
       <c r="F417" t="s">
-        <v>1796</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -16595,10 +16614,10 @@
         <v>1204</v>
       </c>
       <c r="E418" t="s">
-        <v>1797</v>
+        <v>1752</v>
       </c>
       <c r="F418" t="s">
-        <v>1798</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -16615,10 +16634,10 @@
         <v>1204</v>
       </c>
       <c r="E419" t="s">
-        <v>1799</v>
+        <v>1754</v>
       </c>
       <c r="F419" t="s">
-        <v>1800</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -16635,10 +16654,10 @@
         <v>1204</v>
       </c>
       <c r="E420" t="s">
-        <v>1801</v>
+        <v>1756</v>
       </c>
       <c r="F420" t="s">
-        <v>1922</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -16655,10 +16674,10 @@
         <v>1204</v>
       </c>
       <c r="E421" t="s">
-        <v>1802</v>
+        <v>1757</v>
       </c>
       <c r="F421" t="s">
-        <v>1803</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -16675,10 +16694,10 @@
         <v>1204</v>
       </c>
       <c r="E422" t="s">
-        <v>1804</v>
+        <v>1759</v>
       </c>
       <c r="F422" t="s">
-        <v>1805</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -16695,10 +16714,10 @@
         <v>1204</v>
       </c>
       <c r="E423" t="s">
-        <v>1806</v>
+        <v>1761</v>
       </c>
       <c r="F423" t="s">
-        <v>1807</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -16715,10 +16734,10 @@
         <v>1204</v>
       </c>
       <c r="E424" t="s">
-        <v>1808</v>
+        <v>1763</v>
       </c>
       <c r="F424" t="s">
-        <v>1809</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -16735,10 +16754,10 @@
         <v>1204</v>
       </c>
       <c r="E425" t="s">
-        <v>1810</v>
+        <v>1765</v>
       </c>
       <c r="F425" t="s">
-        <v>1811</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -16755,10 +16774,10 @@
         <v>1204</v>
       </c>
       <c r="E426" t="s">
-        <v>1812</v>
+        <v>1767</v>
       </c>
       <c r="F426" t="s">
-        <v>1813</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -16775,10 +16794,10 @@
         <v>1204</v>
       </c>
       <c r="E427" t="s">
-        <v>1814</v>
+        <v>1769</v>
       </c>
       <c r="F427" t="s">
-        <v>1815</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -16795,10 +16814,10 @@
         <v>1204</v>
       </c>
       <c r="E428" t="s">
-        <v>1816</v>
+        <v>1771</v>
       </c>
       <c r="F428" t="s">
-        <v>1817</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -16815,10 +16834,10 @@
         <v>1204</v>
       </c>
       <c r="E429" t="s">
-        <v>1818</v>
+        <v>1773</v>
       </c>
       <c r="F429" t="s">
-        <v>1819</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -16835,10 +16854,10 @@
         <v>1204</v>
       </c>
       <c r="E430" t="s">
-        <v>1820</v>
+        <v>1775</v>
       </c>
       <c r="F430" t="s">
-        <v>1821</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -16855,10 +16874,10 @@
         <v>1204</v>
       </c>
       <c r="E431" t="s">
-        <v>1822</v>
+        <v>1777</v>
       </c>
       <c r="F431" t="s">
-        <v>1823</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -16875,10 +16894,10 @@
         <v>1204</v>
       </c>
       <c r="E432" t="s">
-        <v>1824</v>
+        <v>1779</v>
       </c>
       <c r="F432" t="s">
-        <v>1725</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -16895,10 +16914,10 @@
         <v>1204</v>
       </c>
       <c r="E433" t="s">
-        <v>1825</v>
+        <v>1780</v>
       </c>
       <c r="F433" t="s">
-        <v>1826</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -16915,10 +16934,10 @@
         <v>1204</v>
       </c>
       <c r="E434" t="s">
-        <v>1827</v>
+        <v>1782</v>
       </c>
       <c r="F434" t="s">
-        <v>1828</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -16935,10 +16954,10 @@
         <v>1204</v>
       </c>
       <c r="E435" t="s">
-        <v>1829</v>
+        <v>1784</v>
       </c>
       <c r="F435" t="s">
-        <v>1830</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -16955,10 +16974,10 @@
         <v>1204</v>
       </c>
       <c r="E436" t="s">
-        <v>1831</v>
+        <v>1786</v>
       </c>
       <c r="F436" t="s">
-        <v>1832</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -16975,10 +16994,10 @@
         <v>1204</v>
       </c>
       <c r="E437" t="s">
-        <v>1833</v>
+        <v>1788</v>
       </c>
       <c r="F437" t="s">
-        <v>1834</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -16995,10 +17014,10 @@
         <v>1204</v>
       </c>
       <c r="E438" t="s">
-        <v>1835</v>
+        <v>1790</v>
       </c>
       <c r="F438" t="s">
-        <v>1923</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -17015,10 +17034,10 @@
         <v>1204</v>
       </c>
       <c r="E439" t="s">
-        <v>1836</v>
+        <v>1791</v>
       </c>
       <c r="F439" t="s">
-        <v>1837</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -17035,10 +17054,10 @@
         <v>1204</v>
       </c>
       <c r="E440" t="s">
-        <v>1838</v>
+        <v>1793</v>
       </c>
       <c r="F440" t="s">
-        <v>1839</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -17055,10 +17074,10 @@
         <v>1204</v>
       </c>
       <c r="E441" t="s">
-        <v>1840</v>
+        <v>1795</v>
       </c>
       <c r="F441" t="s">
-        <v>1841</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -17075,10 +17094,10 @@
         <v>1204</v>
       </c>
       <c r="E442" t="s">
-        <v>1842</v>
+        <v>1797</v>
       </c>
       <c r="F442" t="s">
-        <v>1843</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -17095,10 +17114,10 @@
         <v>1204</v>
       </c>
       <c r="E443" t="s">
-        <v>1844</v>
+        <v>1799</v>
       </c>
       <c r="F443" t="s">
-        <v>1845</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -17115,10 +17134,10 @@
         <v>1204</v>
       </c>
       <c r="E444" t="s">
-        <v>1846</v>
+        <v>1801</v>
       </c>
       <c r="F444" t="s">
-        <v>1924</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -17135,10 +17154,10 @@
         <v>1204</v>
       </c>
       <c r="E445" t="s">
-        <v>1847</v>
+        <v>1802</v>
       </c>
       <c r="F445" t="s">
-        <v>1848</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -17155,10 +17174,10 @@
         <v>1204</v>
       </c>
       <c r="E446" t="s">
-        <v>1849</v>
+        <v>1804</v>
       </c>
       <c r="F446" t="s">
-        <v>1850</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -17175,10 +17194,10 @@
         <v>1204</v>
       </c>
       <c r="E447" t="s">
-        <v>1851</v>
+        <v>1806</v>
       </c>
       <c r="F447" t="s">
-        <v>1852</v>
+        <v>1807</v>
       </c>
     </row>
   </sheetData>
@@ -17248,7 +17267,7 @@
         <v>1392</v>
       </c>
       <c r="F2" t="s">
-        <v>1853</v>
+        <v>1808</v>
       </c>
       <c r="G2" t="s">
         <v>1393</v>
@@ -17397,7 +17416,7 @@
         <v>1421</v>
       </c>
       <c r="F9" t="s">
-        <v>1854</v>
+        <v>1809</v>
       </c>
       <c r="G9" t="s">
         <v>1422</v>
@@ -17460,7 +17479,7 @@
         <v>1433</v>
       </c>
       <c r="F12" t="s">
-        <v>1855</v>
+        <v>1810</v>
       </c>
       <c r="G12" t="s">
         <v>1410</v>
@@ -17615,7 +17634,7 @@
         <v>1461</v>
       </c>
       <c r="F19" t="s">
-        <v>1856</v>
+        <v>1811</v>
       </c>
       <c r="G19" t="s">
         <v>1410</v>
@@ -17744,7 +17763,7 @@
         <v>1482</v>
       </c>
       <c r="F25" t="s">
-        <v>1857</v>
+        <v>1812</v>
       </c>
       <c r="G25" t="s">
         <v>1465</v>
@@ -17973,7 +17992,7 @@
         <v>924</v>
       </c>
       <c r="D36" t="s">
-        <v>1858</v>
+        <v>1813</v>
       </c>
       <c r="E36" t="s">
         <v>1523</v>
@@ -18025,7 +18044,7 @@
         <v>1532</v>
       </c>
       <c r="G38" t="s">
-        <v>1859</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18039,7 +18058,7 @@
         <v>924</v>
       </c>
       <c r="D39" t="s">
-        <v>1860</v>
+        <v>1815</v>
       </c>
       <c r="E39" t="s">
         <v>1534</v>
@@ -18059,16 +18078,16 @@
         <v>1204</v>
       </c>
       <c r="D40" t="s">
-        <v>1861</v>
+        <v>1816</v>
       </c>
       <c r="E40" t="s">
-        <v>1862</v>
+        <v>1817</v>
       </c>
       <c r="F40" t="s">
-        <v>1863</v>
+        <v>1818</v>
       </c>
       <c r="G40" t="s">
-        <v>1864</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18082,13 +18101,13 @@
         <v>1204</v>
       </c>
       <c r="D41" t="s">
-        <v>1865</v>
+        <v>1820</v>
       </c>
       <c r="E41" t="s">
-        <v>1866</v>
+        <v>1821</v>
       </c>
       <c r="G41" t="s">
-        <v>1867</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18113,13 +18132,13 @@
         <v>1204</v>
       </c>
       <c r="D43" t="s">
-        <v>1868</v>
+        <v>1823</v>
       </c>
       <c r="E43" t="s">
-        <v>1869</v>
+        <v>1878</v>
       </c>
       <c r="F43" t="s">
-        <v>1870</v>
+        <v>1824</v>
       </c>
       <c r="G43" t="s">
         <v>1521</v>
@@ -18136,16 +18155,16 @@
         <v>1204</v>
       </c>
       <c r="D44" t="s">
-        <v>1871</v>
+        <v>1825</v>
       </c>
       <c r="E44" t="s">
-        <v>1872</v>
+        <v>1826</v>
       </c>
       <c r="F44" t="s">
-        <v>1873</v>
+        <v>1827</v>
       </c>
       <c r="G44" t="s">
-        <v>1874</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18159,13 +18178,13 @@
         <v>1204</v>
       </c>
       <c r="D45" t="s">
-        <v>1875</v>
+        <v>1829</v>
       </c>
       <c r="E45" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
       <c r="F45" t="s">
-        <v>1870</v>
+        <v>1824</v>
       </c>
       <c r="G45" t="s">
         <v>1521</v>
@@ -18182,13 +18201,13 @@
         <v>1204</v>
       </c>
       <c r="D46" t="s">
-        <v>1877</v>
+        <v>1830</v>
       </c>
       <c r="E46" t="s">
-        <v>1878</v>
+        <v>1831</v>
       </c>
       <c r="G46" t="s">
-        <v>1889</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18202,16 +18221,16 @@
         <v>1204</v>
       </c>
       <c r="D47" t="s">
-        <v>1879</v>
+        <v>1832</v>
       </c>
       <c r="E47" t="s">
-        <v>1880</v>
+        <v>1833</v>
       </c>
       <c r="F47" t="s">
-        <v>1881</v>
+        <v>1834</v>
       </c>
       <c r="G47" t="s">
-        <v>1882</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18225,16 +18244,16 @@
         <v>1204</v>
       </c>
       <c r="D48" t="s">
-        <v>1883</v>
+        <v>1836</v>
       </c>
       <c r="E48" t="s">
-        <v>1884</v>
+        <v>1837</v>
       </c>
       <c r="F48" t="s">
-        <v>1873</v>
+        <v>1827</v>
       </c>
       <c r="G48" t="s">
-        <v>1874</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18248,13 +18267,13 @@
         <v>1204</v>
       </c>
       <c r="D49" t="s">
-        <v>1885</v>
+        <v>1838</v>
       </c>
       <c r="E49" t="s">
-        <v>1886</v>
+        <v>1880</v>
       </c>
       <c r="F49" t="s">
-        <v>1870</v>
+        <v>1824</v>
       </c>
       <c r="G49" t="s">
         <v>1521</v>
@@ -18271,10 +18290,10 @@
         <v>1204</v>
       </c>
       <c r="D50" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="E50" t="s">
-        <v>1888</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -18345,8 +18364,8 @@
       <c r="A2">
         <v>2000</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>1549</v>
+      <c r="B2" s="14" t="s">
+        <v>1882</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
@@ -18358,8 +18377,8 @@
       <c r="A3">
         <v>2001</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>1550</v>
+      <c r="B3" s="14" t="s">
+        <v>1883</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>13</v>
@@ -18371,8 +18390,8 @@
       <c r="A4">
         <v>2002</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>1551</v>
+      <c r="B4" s="14" t="s">
+        <v>1884</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>13</v>
@@ -18384,8 +18403,8 @@
       <c r="A5">
         <v>2013</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>1552</v>
+      <c r="B5" s="14" t="s">
+        <v>1885</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -18397,8 +18416,8 @@
       <c r="A6">
         <v>2014</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>1553</v>
+      <c r="B6" s="14" t="s">
+        <v>1886</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>13</v>
@@ -18410,8 +18429,8 @@
       <c r="A7">
         <v>2017</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>1554</v>
+      <c r="B7" s="14" t="s">
+        <v>1887</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
@@ -18423,8 +18442,8 @@
       <c r="A8">
         <v>2010</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>1555</v>
+      <c r="B8" s="14" t="s">
+        <v>1888</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>13</v>
@@ -18436,8 +18455,8 @@
       <c r="A9">
         <v>2008</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>1556</v>
+      <c r="B9" s="14" t="s">
+        <v>1889</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>13</v>
@@ -18449,8 +18468,8 @@
       <c r="A10">
         <v>2021</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>1557</v>
+      <c r="B10" s="14" t="s">
+        <v>1890</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>13</v>
@@ -18462,8 +18481,8 @@
       <c r="A11">
         <v>2022</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>1558</v>
+      <c r="B11" s="14" t="s">
+        <v>1891</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>13</v>
@@ -18475,8 +18494,8 @@
       <c r="A12">
         <v>2012</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>1559</v>
+      <c r="B12" s="14" t="s">
+        <v>1892</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>13</v>
@@ -18488,8 +18507,8 @@
       <c r="A13">
         <v>2011</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>1560</v>
+      <c r="B13" s="14" t="s">
+        <v>1893</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>13</v>
@@ -18501,8 +18520,8 @@
       <c r="A14">
         <v>2015</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>1561</v>
+      <c r="B14" s="14" t="s">
+        <v>1894</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>13</v>
@@ -18514,8 +18533,8 @@
       <c r="A15">
         <v>2016</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>1562</v>
+      <c r="B15" s="14" t="s">
+        <v>1895</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>13</v>
@@ -18527,8 +18546,8 @@
       <c r="A16">
         <v>2023</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>1563</v>
+      <c r="B16" s="14" t="s">
+        <v>1896</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>13</v>
@@ -18540,8 +18559,8 @@
       <c r="A17">
         <v>2024</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>1564</v>
+      <c r="B17" s="14" t="s">
+        <v>1897</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>13</v>
@@ -18553,8 +18572,8 @@
       <c r="A18">
         <v>2020</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>1565</v>
+      <c r="B18" s="14" t="s">
+        <v>1898</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>78</v>
@@ -18566,8 +18585,8 @@
       <c r="A19">
         <v>2003</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>1566</v>
+      <c r="B19" s="14" t="s">
+        <v>1549</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>78</v>
@@ -18579,8 +18598,8 @@
       <c r="A20">
         <v>2004</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>1567</v>
+      <c r="B20" s="14" t="s">
+        <v>1899</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>78</v>
@@ -18592,8 +18611,8 @@
       <c r="A21">
         <v>2006</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>1568</v>
+      <c r="B21" s="14" t="s">
+        <v>1900</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>78</v>
@@ -18605,8 +18624,8 @@
       <c r="A22">
         <v>2005</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>1569</v>
+      <c r="B22" s="14" t="s">
+        <v>1901</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>78</v>
@@ -18618,8 +18637,8 @@
       <c r="A23">
         <v>2018</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>1570</v>
+      <c r="B23" s="14" t="s">
+        <v>1902</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>78</v>
@@ -18631,8 +18650,8 @@
       <c r="A24">
         <v>2009</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>1571</v>
+      <c r="B24" s="14" t="s">
+        <v>1903</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>78</v>
@@ -18644,8 +18663,8 @@
       <c r="A25">
         <v>2025</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>1572</v>
+      <c r="B25" s="14" t="s">
+        <v>1904</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>78</v>
@@ -18657,8 +18676,8 @@
       <c r="A26">
         <v>2007</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>1573</v>
+      <c r="B26" s="14" t="s">
+        <v>1905</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>78</v>
@@ -18670,8 +18689,8 @@
       <c r="A27">
         <v>2019</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>1574</v>
+      <c r="B27" s="14" t="s">
+        <v>1906</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>78</v>
@@ -18682,14 +18701,14 @@
       <c r="A28">
         <v>2031</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>1575</v>
+      <c r="B28" s="14" t="s">
+        <v>1907</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1576</v>
+        <v>1550</v>
       </c>
       <c r="F28" s="6"/>
     </row>
@@ -18697,14 +18716,14 @@
       <c r="A29">
         <v>2030</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>1577</v>
+      <c r="B29" s="14" t="s">
+        <v>1908</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1578</v>
+        <v>1551</v>
       </c>
       <c r="F29" s="6"/>
     </row>
@@ -18712,14 +18731,14 @@
       <c r="A30">
         <v>2033</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>1579</v>
+      <c r="B30" s="14" t="s">
+        <v>1909</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>1580</v>
+        <v>1552</v>
       </c>
       <c r="F30" s="6"/>
     </row>
@@ -18727,14 +18746,14 @@
       <c r="A31">
         <v>2032</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>1581</v>
+      <c r="B31" s="14" t="s">
+        <v>1910</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E31" t="s">
-        <v>1582</v>
+        <v>1553</v>
       </c>
       <c r="F31" s="6"/>
     </row>
@@ -18742,14 +18761,14 @@
       <c r="A32">
         <v>2026</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>1583</v>
+      <c r="B32" s="14" t="s">
+        <v>1911</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E32" t="s">
-        <v>1584</v>
+        <v>1554</v>
       </c>
       <c r="F32" s="6"/>
     </row>
@@ -18757,14 +18776,14 @@
       <c r="A33">
         <v>2027</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>1585</v>
+      <c r="B33" s="14" t="s">
+        <v>1912</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E33" t="s">
-        <v>1586</v>
+        <v>1555</v>
       </c>
       <c r="F33" s="6"/>
     </row>
@@ -18772,14 +18791,14 @@
       <c r="A34">
         <v>2029</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>1587</v>
+      <c r="B34" s="14" t="s">
+        <v>1913</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>1588</v>
+        <v>1556</v>
       </c>
       <c r="F34" s="6"/>
     </row>
@@ -18787,14 +18806,14 @@
       <c r="A35">
         <v>2028</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>1589</v>
+      <c r="B35" s="14" t="s">
+        <v>1914</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>924</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>1590</v>
+        <v>1557</v>
       </c>
       <c r="F35" s="6"/>
     </row>
@@ -18802,8 +18821,8 @@
       <c r="A36">
         <v>2043</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>1591</v>
+      <c r="B36" s="15" t="s">
+        <v>1915</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>1204</v>
@@ -18816,8 +18835,8 @@
       <c r="A37">
         <v>2040</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>1592</v>
+      <c r="B37" s="14" t="s">
+        <v>1916</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>1204</v>
@@ -18830,8 +18849,8 @@
       <c r="A38">
         <v>2035</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>1593</v>
+      <c r="B38" s="14" t="s">
+        <v>1917</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>1204</v>
@@ -18844,8 +18863,8 @@
       <c r="A39">
         <v>2041</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>1594</v>
+      <c r="B39" s="14" t="s">
+        <v>1918</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>1204</v>
@@ -18858,8 +18877,8 @@
       <c r="A40">
         <v>2042</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>1595</v>
+      <c r="B40" s="14" t="s">
+        <v>1919</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>1204</v>
@@ -18872,8 +18891,8 @@
       <c r="A41">
         <v>2044</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>1596</v>
+      <c r="B41" s="14" t="s">
+        <v>1920</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>1204</v>
@@ -18886,8 +18905,8 @@
       <c r="A42">
         <v>2036</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>1597</v>
+      <c r="B42" s="14" t="s">
+        <v>1921</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>1204</v>
@@ -18900,8 +18919,8 @@
       <c r="A43">
         <v>2034</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>1598</v>
+      <c r="B43" s="14" t="s">
+        <v>1922</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>1204</v>
@@ -18914,8 +18933,8 @@
       <c r="A44">
         <v>2037</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>1599</v>
+      <c r="B44" s="14" t="s">
+        <v>1923</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>1204</v>
@@ -18928,8 +18947,8 @@
       <c r="A45">
         <v>2038</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>1600</v>
+      <c r="B45" s="14" t="s">
+        <v>1924</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>1204</v>
@@ -18942,8 +18961,8 @@
       <c r="A46">
         <v>2039</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>1601</v>
+      <c r="B46" s="14" t="s">
+        <v>1925</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>1204</v>
@@ -18956,8 +18975,8 @@
       <c r="A47">
         <v>2045</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>1602</v>
+      <c r="B47" s="14" t="s">
+        <v>1926</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>1204</v>
@@ -18991,55 +19010,55 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1603</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1604</v>
+        <v>1559</v>
       </c>
       <c r="B2" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1606</v>
+        <v>1561</v>
       </c>
       <c r="B3" t="s">
-        <v>1607</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1608</v>
+        <v>1563</v>
       </c>
       <c r="B4" t="s">
-        <v>1609</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="B5" t="s">
-        <v>1611</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="B6" t="s">
-        <v>1613</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1614</v>
+        <v>1569</v>
       </c>
       <c r="B7" t="s">
-        <v>1615</v>
+        <v>1570</v>
       </c>
     </row>
   </sheetData>
@@ -19065,12 +19084,12 @@
         <v>1387</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1616</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1617</v>
+        <v>1572</v>
       </c>
       <c r="B2" t="b">
         <f>FALSE()</f>
